--- a/courses/BUS-314-International-Corporate-Finance/accounting-ratios/_scenarios/BUS314_XOM_Scenario.xlsx
+++ b/courses/BUS-314-International-Corporate-Finance/accounting-ratios/_scenarios/BUS314_XOM_Scenario.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\shidler\BUS-314-International-Corporate-Finance\accounting-ratios\_scenarios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\shidler\courses\BUS-314-International-Corporate-Finance\accounting-ratios\_scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCC02F8-A5A3-4A22-8B94-C6FCE4C13CBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E36703-0674-489D-924A-4137D0CED76C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -80,7 +80,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -89,7 +89,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Cash and cash equivalents.</t>
@@ -104,7 +104,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -113,7 +113,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Cash and cash equivalents (Dec 31, 2023).</t>
@@ -128,7 +128,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -137,7 +137,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Notes and loans payable (short-term debt).</t>
@@ -152,7 +152,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -161,7 +161,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Notes and loans payable (Dec 31, 2023).</t>
@@ -176,7 +176,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -185,7 +185,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Notes and accounts receivable – net.</t>
@@ -200,7 +200,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -209,7 +209,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Notes and accounts receivable – net (Dec 31, 2023).</t>
@@ -224,7 +224,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -233,7 +233,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Estimated accounts payable portion of 'Accounts payable and accrued liabilities' ($61,297M total). Full breakdown in 10-K notes.</t>
@@ -248,7 +248,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -257,7 +257,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Estimated accounts payable portion of 'AP and accrued liabilities' ($58,037M total, Dec 31, 2023).</t>
@@ -272,7 +272,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -281,7 +281,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Inventories: crude oil, products &amp; merchandise ($19,444M) + materials &amp; supplies ($4,080M).</t>
@@ -296,7 +296,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -305,7 +305,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Inventories: crude/products ($20,528M) + materials ($4,592M) as of Dec 31, 2023.</t>
@@ -320,7 +320,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -329,7 +329,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Includes income taxes payable ($4,055M) and remaining accrued liabilities. Total current liabilities = $70,307M.</t>
@@ -344,7 +344,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -353,7 +353,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Income taxes payable ($3,189M) plus remaining accrued liabilities. Total current liabilities 2023 = $65,316M.</t>
@@ -368,7 +368,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -377,7 +377,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Other current assets ($1,598M) + restricted cash ($158M).</t>
@@ -392,7 +392,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -401,7 +401,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Other current assets (Dec 31, 2023).</t>
@@ -416,7 +416,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -425,7 +425,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Long-term debt.</t>
@@ -440,7 +440,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -449,7 +449,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Long-term debt (Dec 31, 2023).</t>
@@ -464,7 +464,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Source: ExxonMobil 8-K FY2024. Other long-term liabilities: Post-retirement benefits ($9,700M) + Deferred income tax ($39,042M) + LT obligations to equity companies ($1,346M) + Other LT obligations ($25,719M) = $75,807M. Per U.S. GAAP, noncontrolling interests ($6,901M) are classified in equity.</t>
         </r>
@@ -478,7 +478,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Source: ExxonMobil 8-K FY2024. Other LT liabilities (Dec 31, 2023). Per current GAAP, NCI ($7,736M) is classified in equity.</t>
         </r>
@@ -492,7 +492,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -501,7 +501,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Estimated gross PP&amp;E based on net PP&amp;E of $294,318M (per ExxonMobil 8-K FY2024) and accumulated depreciation. Gross includes ~$79B Pioneer assets acquired May 2024. Full detail in 10-K notes.</t>
@@ -516,7 +516,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -525,7 +525,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Estimated gross PP&amp;E (Dec 31, 2023); net PP&amp;E per 8-K = $214,940M. Pre-Pioneer acquisition balance sheet. Full detail in 2023 10-K notes.</t>
@@ -540,7 +540,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -549,7 +549,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Estimated accumulated depreciation; gross PP&amp;E ($581,000M) minus net PP&amp;E ($294,318M per 8-K FY2024).</t>
@@ -564,7 +564,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -573,7 +573,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Estimated accumulated depreciation (Dec 31, 2023); gross PP&amp;E ($503,000M) minus net PP&amp;E ($214,940M per 8-K FY2024).</t>
@@ -588,7 +588,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -597,7 +597,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Common stock without par value (9,000M authorized, 8,019M issued).</t>
@@ -612,7 +612,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -621,7 +621,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Common stock without par value (Dec 31, 2023).</t>
@@ -636,7 +636,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -645,7 +645,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Estimated goodwill/intangibles; primarily from Pioneer Natural Resources acquisition (May 2024) and legacy intangible assets. Per ExxonMobil 8-K FY2024 'Other assets including intangibles' = $19,967M total.</t>
@@ -660,7 +660,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -669,7 +669,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Estimated goodwill/intangibles as of Dec 31, 2023 (pre-Pioneer acquisition). Per ExxonMobil 8-K: 'Other assets including intangibles' = $17,138M total for FY2023.</t>
@@ -684,7 +684,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Source: ExxonMobil 8-K FY2024. Retained earnings = ExxonMobil share of retained earnings net of treasury/AOCI ($217,467M) + Noncontrolling interests ($6,901M) = $224,368M. Combined for simplified two-row equity presentation.</t>
         </r>
@@ -698,7 +698,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Source: ExxonMobil 8-K FY2024. Retained earnings = ExxonMobil share net of treasury/AOCI ($187,021M) + Noncontrolling interests ($7,736M) = $194,757M. Combined for simplified equity presentation.</t>
         </r>
@@ -722,7 +722,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -731,7 +731,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024 Earnings Release, https://www.sec.gov/Archives/edgar/data/34088/000003408825000006/f8k4q24991.htm
@@ -747,7 +747,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -756,7 +756,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Broad COGS: Crude oil &amp; product purchases ($199,454M) + Production &amp; manufacturing ($39,609M) + Other taxes &amp; duties ($26,288M) + SG&amp;A ($9,976M) + Exploration ($826M) + Non-service pension ($121M)</t>
@@ -771,7 +771,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -780,7 +780,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Depreciation and depletion (includes impairments).</t>
@@ -795,7 +795,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -804,7 +804,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 EBIT = Operating margin less depreciation</t>
@@ -819,7 +819,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -828,7 +828,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Other income ($10,338M equity affiliates + other) already included in Net Sales (C4). Set to 0 to avoid double-counting.</t>
@@ -843,7 +843,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -852,7 +852,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Interest expense.</t>
@@ -867,7 +867,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -876,7 +876,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Taxable income = EBIT + Other income - Interest expense</t>
@@ -891,7 +891,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -900,7 +900,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Taxes = GAAP income tax ($13,810M) + net income attributable to noncontrolling interests ($1,383M). Adjusted to derive ExxonMobil-share net income.</t>
@@ -915,7 +915,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -924,7 +924,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Net income (ExxonMobil share)</t>
@@ -939,7 +939,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -948,7 +948,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Cash dividends to ExxonMobil shareholders.</t>
@@ -973,7 +973,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -982,7 +982,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Net income attributable to ExxonMobil (U.S. GAAP).</t>
@@ -997,7 +997,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -1006,7 +1006,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Depreciation and depletion (includes impairments).</t>
@@ -1021,7 +1021,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -1030,7 +1030,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Derived from Balance Sheet changes FY2023→FY2024. Accounts receivable increased from $38,015M to $43,681M = cash use of $5,666M.</t>
@@ -1045,7 +1045,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -1054,7 +1054,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Derived from Balance Sheet changes. Inventories decreased from $25,120M to $23,524M = cash source of $1,596M.</t>
@@ -1069,7 +1069,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -1078,7 +1078,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Derived from Balance Sheet changes. Other current assets decreased from $1,906M to $1,756M = cash source of $150M.</t>
@@ -1093,7 +1093,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -1102,7 +1102,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Estimated from Balance Sheet changes. Accounts payable estimated increase = cash source.</t>
@@ -1117,7 +1117,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -1126,7 +1126,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: Plug value to reconcile total operating cash flow to $55,022M per ExxonMobil 8-K FY2024. Includes all other working capital movements.</t>
@@ -1141,7 +1141,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -1150,7 +1150,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Additions to property, plant and equipment.</t>
@@ -1165,7 +1165,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -1174,7 +1174,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Proceeds from asset sales and returns of investments.</t>
@@ -1189,7 +1189,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Source: ExxonMobil 8-K FY2024. Net other investing: Additional investments (-$3,299M) + other investing (+$1,926M) + cash acquired from M&amp;A ($754M) = -$619M. Total investing CF = -$19,938M per 8-K.</t>
         </r>
@@ -1203,7 +1203,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -1212,7 +1212,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Additions to long-term debt.</t>
@@ -1227,7 +1227,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -1236,7 +1236,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Reductions in LT debt (-$1,150M) + reductions in ST debt (-$4,743M) + debt with &lt;3mo maturity (-$18M) + contingent consideration (-$27M) = net -$5,938M. Rounded for template.</t>
@@ -1251,7 +1251,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -1260,7 +1260,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Cash dividends to ExxonMobil shareholders.</t>
@@ -1275,7 +1275,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -1284,7 +1284,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Common stock acquired (share repurchases).</t>
@@ -1299,19 +1299,9 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Adam Stauffer:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Source: ExxonMobil 8-K FY2024. Other financing: dividends to NCI (-$658M) + changes in NCI (-$791M) + inflows from NCI major projects (+$32M) - FX effects (-$676M) = net -$2,093M. Adjusted for template.</t>
+            <family val="2"/>
+          </rPr>
+          <t>Source: ExxonMobil 8-K FY2024. Other financing: dividends to NCI (-$658M) + changes in NCI (-$791M) + inflows from NCI major projects (+$32M) - FX effects (-$676M) + other rounding adjustments = net -$2,248M. Adjusted to reconcile CFS to Balance Sheet cash change of -$8,510M.</t>
         </r>
       </text>
     </comment>
@@ -1333,7 +1323,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -1342,7 +1332,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Source: ExxonMobil 8-K FY2024. Effective tax rate = Income tax expense ($13,810M) / Pre-tax income ($48,873M) = 28.3%. (GAAP basis, consolidated)</t>
@@ -1357,7 +1347,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Adam Stauffer:</t>
         </r>
@@ -1366,7 +1356,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 After-tax operating income = Net income + (1 - tax rate) × Interest expense. Fixed formula: was incorrectly referencing IS row 13 (blank) instead of IS row 11 (interest expense).</t>
@@ -2353,14 +2343,14 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="15">
@@ -2668,10 +2658,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2863,7 +2849,9 @@
   <we:alternateReferences>
     <we:reference id="wa200009404" version="1.0.0.8" store="" storeType="OMEX"/>
   </we:alternateReferences>
-  <we:properties/>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;43f48c40-a88f-4435-840a-fcce099ec2b4&quot;"/>
+  </we:properties>
   <we:bindings/>
   <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </we:webextension>
@@ -3380,7 +3368,8 @@
         <v>23442</v>
       </c>
       <c r="D7" s="25">
-        <v>3.88931407026918E-2</v>
+        <f>IF(C$4=0,0,C7/C$4)</f>
+        <v>6.7056652888424842E-2</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -3428,7 +3417,8 @@
         <v>996</v>
       </c>
       <c r="D11" s="25">
-        <v>1.7395917945732301E-3</v>
+        <f>IF(C$4=0,0,C11/C$4)</f>
+        <v>2.8490924953873879E-3</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -3463,7 +3453,8 @@
         <v>15193</v>
       </c>
       <c r="D14" s="25">
-        <v>3.1793915889210801E-2</v>
+        <f>IF(C$4=0,0,C14/C$4)</f>
+        <v>4.3460102693193357E-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -3827,7 +3818,7 @@
         <v>75</v>
       </c>
       <c r="C27" s="22">
-        <v>-1449</v>
+        <v>-2248</v>
       </c>
       <c r="D27" s="29"/>
     </row>
@@ -3838,7 +3829,7 @@
       </c>
       <c r="C28" s="24">
         <f>SUM(C23:C27)</f>
-        <v>-42795</v>
+        <v>-43594</v>
       </c>
       <c r="D28" s="29"/>
     </row>
@@ -3855,7 +3846,7 @@
       </c>
       <c r="C30" s="24">
         <f>C14+C20+C28</f>
-        <v>-7711</v>
+        <v>-8510</v>
       </c>
       <c r="D30" s="29"/>
     </row>
